--- a/data/trans_camb/P16-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P16-Provincia-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>8,89; 25,58</t>
+          <t>9,95; 25,73</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>10,55; 27,72</t>
+          <t>10,59; 27,11</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15,88; 33,94</t>
+          <t>16,26; 33,3</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10,46; 26,36</t>
+          <t>10,07; 26,75</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,3; 19,01</t>
+          <t>2,26; 18,94</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,8; 23,94</t>
+          <t>8,09; 23,55</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,06; 23,76</t>
+          <t>12,1; 24,05</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>9,42; 21,26</t>
+          <t>9,35; 20,7</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>13,4; 26,51</t>
+          <t>14,45; 26,09</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>20,2; 73,46</t>
+          <t>22,07; 73,2</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>24,12; 81,65</t>
+          <t>22,72; 76,75</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>36,04; 96,69</t>
+          <t>37,46; 94,58</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16,43; 49,53</t>
+          <t>16,13; 49,74</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,6; 35,08</t>
+          <t>3,65; 36,16</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,93; 45,06</t>
+          <t>12,6; 44,53</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,06; 52,11</t>
+          <t>22,79; 53,33</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>17,8; 47,3</t>
+          <t>18,01; 45,19</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>25,68; 58,4</t>
+          <t>27,97; 57,51</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,87; 19,46</t>
+          <t>6,15; 19,24</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,62; 16,38</t>
+          <t>3,18; 16,53</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,79; 18,59</t>
+          <t>3,99; 18,98</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7,48; 19,09</t>
+          <t>7,14; 19,08</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,81; 14,37</t>
+          <t>2,39; 14,17</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 12,12</t>
+          <t>0,32; 12,01</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,54; 17,52</t>
+          <t>8,06; 17,18</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5,18; 13,66</t>
+          <t>5,11; 13,88</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,63; 13,35</t>
+          <t>4,04; 13,68</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>15,92; 56,64</t>
+          <t>14,34; 54,6</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,66; 47,04</t>
+          <t>7,62; 47,55</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9,43; 53,49</t>
+          <t>9,65; 54,13</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12,18; 34,79</t>
+          <t>11,35; 34,57</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,54; 26,23</t>
+          <t>3,84; 25,26</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 22,04</t>
+          <t>0,61; 22,06</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>16,69; 37,62</t>
+          <t>15,81; 37,43</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10,22; 29,79</t>
+          <t>10,26; 30,69</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,33; 28,82</t>
+          <t>7,28; 29,28</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>10,35; 26,06</t>
+          <t>10,34; 26,18</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,4; 22,27</t>
+          <t>7,41; 22,47</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14,48; 30,16</t>
+          <t>14,6; 29,93</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6,35; 21,23</t>
+          <t>8,12; 22,25</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,73; 11,34</t>
+          <t>-2,56; 11,98</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,57; 15,68</t>
+          <t>0,87; 14,22</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,7; 21,76</t>
+          <t>11,23; 21,77</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>3,94; 14,84</t>
+          <t>3,81; 14,31</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>9,66; 20,78</t>
+          <t>9,6; 19,91</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>25,96; 83,23</t>
+          <t>26,75; 84,37</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>17,97; 68,08</t>
+          <t>18,63; 73,96</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>36,35; 93,78</t>
+          <t>37,43; 97,99</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>9,7; 36,95</t>
+          <t>12,5; 38,94</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-6,37; 19,16</t>
+          <t>-3,9; 20,91</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,9; 27,15</t>
+          <t>1,28; 24,74</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>20,5; 47,38</t>
+          <t>21,89; 47,54</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>7,64; 32,01</t>
+          <t>7,51; 30,72</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>18,65; 45,82</t>
+          <t>18,31; 43,21</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,88; 16,02</t>
+          <t>1,47; 16,09</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>14,59; 28,75</t>
+          <t>13,81; 28,02</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8,62; 26,1</t>
+          <t>7,97; 26,16</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10,06; 23,1</t>
+          <t>9,59; 22,83</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>9,98; 23,3</t>
+          <t>10,47; 23,81</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-4,76; 22,05</t>
+          <t>-5,38; 22,05</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,89; 18,32</t>
+          <t>7,63; 17,59</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>13,78; 23,7</t>
+          <t>13,87; 23,87</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>4,7; 24,05</t>
+          <t>4,41; 23,36</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>4,62; 44,89</t>
+          <t>3,35; 44,74</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>33,7; 81,55</t>
+          <t>30,84; 78,14</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>20,51; 72,22</t>
+          <t>18,57; 71,1</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>16,32; 42,25</t>
+          <t>15,52; 42,49</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>16,45; 43,16</t>
+          <t>17,22; 44,49</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-8,11; 41,38</t>
+          <t>-9,76; 40,18</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>15,09; 39,05</t>
+          <t>14,71; 38,19</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>26,64; 50,97</t>
+          <t>27,11; 52,01</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>8,92; 51,39</t>
+          <t>8,46; 49,82</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,12; 16,02</t>
+          <t>-3,36; 17,06</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-13,32; 5,98</t>
+          <t>-14,29; 6,0</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-8,65; 10,78</t>
+          <t>-8,54; 10,92</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>9,5; 27,46</t>
+          <t>8,81; 26,14</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-7,65; 10,2</t>
+          <t>-7,81; 11,04</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-7,92; 8,79</t>
+          <t>-6,45; 9,17</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,98; 18,85</t>
+          <t>5,73; 19,08</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-7,77; 5,2</t>
+          <t>-7,47; 5,57</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-4,44; 8,29</t>
+          <t>-4,92; 8,13</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-6,02; 38,8</t>
+          <t>-6,65; 40,11</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-26,09; 13,94</t>
+          <t>-27,85; 13,99</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-16,59; 24,94</t>
+          <t>-16,46; 26,0</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>13,67; 47,44</t>
+          <t>12,95; 46,25</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-11,55; 17,55</t>
+          <t>-11,55; 18,92</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-11,34; 15,29</t>
+          <t>-9,45; 16,63</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>8,48; 36,59</t>
+          <t>9,74; 37,32</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-13,09; 9,96</t>
+          <t>-12,67; 10,96</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-7,54; 16,42</t>
+          <t>-8,47; 16,25</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>10,27; 26,72</t>
+          <t>10,08; 26,58</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-2,58; 14,29</t>
+          <t>-3,2; 14,63</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>9,74; 25,76</t>
+          <t>9,74; 25,62</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5,68; 20,86</t>
+          <t>6,42; 21,14</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-9,92; 6,77</t>
+          <t>-8,71; 7,85</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-7,55; 7,66</t>
+          <t>-7,7; 7,56</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10,01; 21,51</t>
+          <t>10,12; 21,57</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-3,67; 9,03</t>
+          <t>-3,62; 8,15</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>2,99; 14,17</t>
+          <t>3,4; 14,92</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>23,2; 73,07</t>
+          <t>22,8; 72,8</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-5,52; 39,13</t>
+          <t>-7,24; 40,64</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>23,33; 71,89</t>
+          <t>21,59; 72,01</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>8,46; 34,91</t>
+          <t>9,59; 35,73</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-14,29; 11,11</t>
+          <t>-12,75; 13,2</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-11,06; 13,0</t>
+          <t>-11,16; 12,68</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>17,9; 43,74</t>
+          <t>18,35; 44,06</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-6,73; 18,37</t>
+          <t>-6,61; 16,6</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>5,3; 28,58</t>
+          <t>6,09; 30,22</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>7,89; 19,58</t>
+          <t>8,09; 19,45</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>0,93; 12,83</t>
+          <t>0,76; 12,04</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>15,07; 27,68</t>
+          <t>15,08; 27,84</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>6,35; 17,69</t>
+          <t>6,61; 17,18</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-4,14; 6,77</t>
+          <t>-4,25; 6,67</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>11,19; 33,22</t>
+          <t>11,37; 34,62</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>8,55; 16,43</t>
+          <t>8,92; 16,63</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>0,1; 8,17</t>
+          <t>-0,07; 7,98</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>15,93; 36,21</t>
+          <t>15,82; 34,18</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>18,66; 56,08</t>
+          <t>19,45; 54,62</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>2,14; 35,61</t>
+          <t>1,86; 33,44</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>35,98; 77,4</t>
+          <t>36,43; 76,6</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>10,75; 33,42</t>
+          <t>11,07; 32,55</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-7,0; 12,93</t>
+          <t>-7,27; 12,66</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>19,86; 63,41</t>
+          <t>19,97; 66,41</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>17,68; 36,78</t>
+          <t>18,13; 37,04</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>0,17; 17,99</t>
+          <t>0,01; 17,62</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>33,0; 76,23</t>
+          <t>32,64; 76,2</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-8,05; 1,99</t>
+          <t>-8,1; 2,03</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 8,54</t>
+          <t>-0,95; 9,04</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-32,87; -4,0</t>
+          <t>-32,47; -3,44</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-2,92; 7,68</t>
+          <t>-3,07; 7,28</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>2,69; 12,29</t>
+          <t>2,39; 12,21</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-9,99; -0,09</t>
+          <t>-10,56; -0,37</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-3,93; 3,35</t>
+          <t>-4,3; 3,21</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>1,71; 9,19</t>
+          <t>1,99; 9,11</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-28,24; -4,58</t>
+          <t>-26,34; -4,09</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-17,1; 4,79</t>
+          <t>-17,32; 4,69</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-3,17; 20,34</t>
+          <t>-2,12; 21,55</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-71,74; -9,09</t>
+          <t>-70,38; -8,22</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-4,9; 14,46</t>
+          <t>-5,08; 13,47</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>4,52; 22,98</t>
+          <t>4,03; 22,47</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-17,01; -0,29</t>
+          <t>-17,64; -0,58</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-7,41; 6,71</t>
+          <t>-8,26; 6,59</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>3,24; 18,77</t>
+          <t>3,78; 18,66</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-53,57; -9,24</t>
+          <t>-52,75; -8,19</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>7,44; 12,38</t>
+          <t>7,47; 12,47</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>6,94; 11,68</t>
+          <t>6,78; 11,73</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-2,69; 13,28</t>
+          <t>-2,13; 13,64</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>9,24; 14,02</t>
+          <t>9,3; 14,03</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>3,73; 8,51</t>
+          <t>3,73; 8,57</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>4,37; 14,35</t>
+          <t>4,11; 13,91</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>9,09; 12,56</t>
+          <t>9,18; 12,61</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>6,16; 9,49</t>
+          <t>6,03; 9,32</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>1,57; 11,91</t>
+          <t>1,74; 11,9</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>17,8; 31,66</t>
+          <t>18,09; 32,01</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>16,35; 29,76</t>
+          <t>16,38; 30,12</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-6,28; 32,95</t>
+          <t>-5,12; 34,21</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>15,46; 24,38</t>
+          <t>15,6; 24,48</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>6,26; 14,95</t>
+          <t>6,23; 15,09</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>7,37; 24,58</t>
+          <t>6,87; 24,0</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>18,04; 25,76</t>
+          <t>18,0; 25,78</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>12,2; 19,39</t>
+          <t>12,01; 19,11</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>3,19; 24,2</t>
+          <t>3,46; 24,17</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P16-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P16-Provincia-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>25,09</t>
+          <t>24,05</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,75</t>
+          <t>14,0</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>20,46</t>
+          <t>19,23</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>9,95; 25,73</t>
+          <t>9,19; 25,91</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>10,59; 27,11</t>
+          <t>10,22; 27,49</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16,26; 33,3</t>
+          <t>15,44; 31,86</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10,07; 26,75</t>
+          <t>9,98; 26,68</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,26; 18,94</t>
+          <t>2,62; 18,95</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,09; 23,55</t>
+          <t>5,91; 20,92</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,1; 24,05</t>
+          <t>11,96; 24,1</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>9,35; 20,7</t>
+          <t>9,15; 21,23</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>14,45; 26,09</t>
+          <t>13,25; 24,7</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>63,4%</t>
+          <t>60,77%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>26,72%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>41,72%</t>
+          <t>39,21%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>22,07; 73,2</t>
+          <t>20,68; 73,14</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>22,72; 76,75</t>
+          <t>23,75; 80,18</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>37,46; 94,58</t>
+          <t>35,42; 92,14</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16,13; 49,74</t>
+          <t>15,51; 49,86</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,65; 36,16</t>
+          <t>4,25; 35,16</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,6; 44,53</t>
+          <t>8,84; 39,06</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,79; 53,33</t>
+          <t>22,68; 53,76</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>18,01; 45,19</t>
+          <t>17,67; 46,76</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>27,97; 57,51</t>
+          <t>25,01; 54,91</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>11,33</t>
+          <t>11,49</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>6,18</t>
+          <t>4,96</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>8,61</t>
+          <t>8,21</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,15; 19,24</t>
+          <t>6,66; 18,83</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,18; 16,53</t>
+          <t>4,27; 16,57</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,99; 18,98</t>
+          <t>4,91; 18,75</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7,14; 19,08</t>
+          <t>7,62; 19,33</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,39; 14,17</t>
+          <t>2,61; 14,84</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,32; 12,01</t>
+          <t>-0,12; 10,84</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,06; 17,18</t>
+          <t>8,36; 17,54</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5,11; 13,88</t>
+          <t>4,96; 13,97</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,04; 13,68</t>
+          <t>3,13; 12,92</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>29,68%</t>
+          <t>30,1%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>16,95%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>14,34; 54,6</t>
+          <t>16,01; 55,14</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,62; 47,55</t>
+          <t>10,19; 47,18</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9,65; 54,13</t>
+          <t>12,45; 54,27</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11,35; 34,57</t>
+          <t>12,47; 35,03</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,84; 25,26</t>
+          <t>4,18; 26,98</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,61; 22,06</t>
+          <t>-0,07; 19,67</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>15,81; 37,43</t>
+          <t>16,46; 38,41</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10,26; 30,69</t>
+          <t>9,95; 30,38</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,28; 29,28</t>
+          <t>6,13; 28,04</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>22,57</t>
+          <t>23,46</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8,02</t>
+          <t>8,67</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>15,24</t>
+          <t>16,06</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>10,34; 26,18</t>
+          <t>9,96; 25,94</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,41; 22,47</t>
+          <t>6,66; 22,21</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14,6; 29,93</t>
+          <t>15,87; 31,39</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8,12; 22,25</t>
+          <t>6,98; 21,48</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,56; 11,98</t>
+          <t>-2,25; 11,51</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,87; 14,22</t>
+          <t>2,49; 15,76</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,23; 21,77</t>
+          <t>11,4; 21,87</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>3,81; 14,31</t>
+          <t>3,5; 14,38</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>9,6; 19,91</t>
+          <t>10,74; 20,95</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>62,75%</t>
+          <t>65,22%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>31,08%</t>
+          <t>32,75%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>26,75; 84,37</t>
+          <t>24,7; 80,45</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>18,63; 73,96</t>
+          <t>15,6; 70,93</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>37,43; 97,99</t>
+          <t>39,72; 98,58</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>12,5; 38,94</t>
+          <t>10,25; 37,01</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-3,9; 20,91</t>
+          <t>-3,41; 20,12</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,28; 24,74</t>
+          <t>3,86; 27,78</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>21,89; 47,54</t>
+          <t>22,05; 47,47</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>7,51; 30,72</t>
+          <t>7,01; 30,96</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>18,31; 43,21</t>
+          <t>20,98; 45,34</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>17,42</t>
+          <t>14,52</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,05</t>
+          <t>6,74</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>13,45</t>
+          <t>10,78</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,47; 16,09</t>
+          <t>1,18; 16,05</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>13,81; 28,02</t>
+          <t>14,43; 28,49</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7,97; 26,16</t>
+          <t>5,49; 22,69</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9,59; 22,83</t>
+          <t>10,23; 23,04</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>10,47; 23,81</t>
+          <t>10,18; 23,43</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-5,38; 22,05</t>
+          <t>-0,62; 13,38</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,63; 17,59</t>
+          <t>7,34; 18,04</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>13,87; 23,87</t>
+          <t>13,72; 23,83</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>4,41; 23,36</t>
+          <t>4,72; 16,01</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>43,65%</t>
+          <t>36,38%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>27,47%</t>
+          <t>22,01%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>3,35; 44,74</t>
+          <t>2,15; 43,86</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>30,84; 78,14</t>
+          <t>32,31; 81,02</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>18,57; 71,1</t>
+          <t>13,08; 62,6</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>15,52; 42,49</t>
+          <t>16,66; 42,62</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>17,22; 44,49</t>
+          <t>16,71; 43,64</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-9,76; 40,18</t>
+          <t>-0,93; 24,81</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>14,71; 38,19</t>
+          <t>14,19; 39,26</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>27,11; 52,01</t>
+          <t>26,23; 51,9</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>8,46; 49,82</t>
+          <t>9,26; 34,66</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>-1,5</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,15</t>
+          <t>-0,95</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>1,71</t>
+          <t>-0,89</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,36; 17,06</t>
+          <t>-4,39; 16,19</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-14,29; 6,0</t>
+          <t>-13,37; 5,97</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-8,54; 10,92</t>
+          <t>-11,09; 7,52</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>8,81; 26,14</t>
+          <t>9,91; 26,94</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-7,81; 11,04</t>
+          <t>-7,7; 10,54</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-6,45; 9,17</t>
+          <t>-8,84; 7,64</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5,73; 19,08</t>
+          <t>5,08; 19,07</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-7,47; 5,57</t>
+          <t>-8,59; 5,58</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-4,92; 8,13</t>
+          <t>-7,11; 5,83</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>-3,18%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>-1,5%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>-1,62%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-6,65; 40,11</t>
+          <t>-7,52; 38,32</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-27,85; 13,99</t>
+          <t>-25,74; 14,8</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-16,46; 26,0</t>
+          <t>-21,2; 18,13</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>12,95; 46,25</t>
+          <t>14,86; 48,26</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-11,55; 18,92</t>
+          <t>-11,25; 18,4</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-9,45; 16,63</t>
+          <t>-12,89; 13,84</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>9,74; 37,32</t>
+          <t>8,68; 37,41</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-12,67; 10,96</t>
+          <t>-14,32; 10,94</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-8,47; 16,25</t>
+          <t>-11,93; 11,58</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>18,0</t>
+          <t>17,05</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,04</t>
+          <t>0,21</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>8,79</t>
+          <t>8,42</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>10,08; 26,58</t>
+          <t>9,59; 27,13</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-3,2; 14,63</t>
+          <t>-3,38; 14,47</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>9,74; 25,62</t>
+          <t>8,71; 24,97</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>6,42; 21,14</t>
+          <t>5,26; 20,23</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-8,71; 7,85</t>
+          <t>-9,88; 6,79</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-7,7; 7,56</t>
+          <t>-7,69; 7,57</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10,12; 21,57</t>
+          <t>10,02; 21,89</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-3,62; 8,15</t>
+          <t>-4,26; 7,82</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>3,4; 14,92</t>
+          <t>3,32; 13,94</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>44,55%</t>
+          <t>42,18%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>15,98%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>22,8; 72,8</t>
+          <t>21,85; 76,67</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-7,24; 40,64</t>
+          <t>-7,63; 39,07</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>21,59; 72,01</t>
+          <t>19,6; 69,76</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>9,59; 35,73</t>
+          <t>7,75; 33,85</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-12,75; 13,2</t>
+          <t>-14,45; 11,05</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-11,16; 12,68</t>
+          <t>-11,25; 12,41</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>18,35; 44,06</t>
+          <t>18,2; 44,96</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-6,61; 16,6</t>
+          <t>-7,76; 15,65</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>6,09; 30,22</t>
+          <t>6,0; 28,25</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>21,37</t>
+          <t>22,28</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>20,71</t>
+          <t>13,38</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>22,12</t>
+          <t>17,82</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>8,09; 19,45</t>
+          <t>8,18; 19,55</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>0,76; 12,04</t>
+          <t>0,77; 12,58</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>15,08; 27,84</t>
+          <t>17,04; 28,17</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>6,61; 17,18</t>
+          <t>6,54; 17,39</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-4,25; 6,67</t>
+          <t>-4,32; 6,78</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>11,37; 34,62</t>
+          <t>8,22; 18,48</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>8,92; 16,63</t>
+          <t>8,97; 17,11</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 7,98</t>
+          <t>-0,0; 8,14</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>15,82; 34,18</t>
+          <t>14,12; 21,92</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>55,17%</t>
+          <t>57,53%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>37,2%</t>
+          <t>24,04%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>46,72%</t>
+          <t>37,62%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>19,45; 54,62</t>
+          <t>20,29; 55,25</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>1,86; 33,44</t>
+          <t>2,24; 34,95</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>36,43; 76,6</t>
+          <t>41,03; 79,43</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>11,07; 32,55</t>
+          <t>11,32; 33,06</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-7,27; 12,66</t>
+          <t>-7,47; 12,98</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>19,97; 66,41</t>
+          <t>14,37; 35,75</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>18,13; 37,04</t>
+          <t>18,07; 38,13</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>0,01; 17,62</t>
+          <t>0,1; 18,53</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>32,64; 76,2</t>
+          <t>28,63; 48,97</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>-16,0</t>
+          <t>-6,94</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>-5,01</t>
+          <t>-6,05</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-12,18</t>
+          <t>-6,53</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-8,1; 2,03</t>
+          <t>-8,34; 2,21</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 9,04</t>
+          <t>-1,17; 8,79</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-32,47; -3,44</t>
+          <t>-12,09; -2,19</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 7,28</t>
+          <t>-2,93; 7,11</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>2,39; 12,21</t>
+          <t>2,21; 12,59</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-10,56; -0,37</t>
+          <t>-10,8; -1,39</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-4,3; 3,21</t>
+          <t>-3,8; 3,45</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>1,99; 9,11</t>
+          <t>2,05; 9,66</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-26,34; -4,09</t>
+          <t>-9,92; -2,61</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>-35,99%</t>
+          <t>-15,6%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>-8,85%</t>
+          <t>-10,69%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-24,01%</t>
+          <t>-12,88%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-17,32; 4,69</t>
+          <t>-17,92; 5,14</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 21,55</t>
+          <t>-2,43; 21,1</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-70,38; -8,22</t>
+          <t>-25,99; -5,22</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-5,08; 13,47</t>
+          <t>-4,98; 13,39</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>4,03; 22,47</t>
+          <t>3,65; 23,18</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-17,64; -0,58</t>
+          <t>-18,36; -2,64</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-8,26; 6,59</t>
+          <t>-7,27; 7,09</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>3,78; 18,66</t>
+          <t>3,85; 19,94</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-52,75; -8,19</t>
+          <t>-19,11; -5,65</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>8,76</t>
+          <t>11,69</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>7,65</t>
+          <t>4,76</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>8,3</t>
+          <t>8,24</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>7,47; 12,47</t>
+          <t>7,44; 12,54</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>6,78; 11,73</t>
+          <t>6,74; 11,61</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 13,64</t>
+          <t>8,98; 14,19</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>9,3; 14,03</t>
+          <t>9,34; 13,89</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>3,73; 8,57</t>
+          <t>3,98; 8,68</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>4,11; 13,91</t>
+          <t>2,65; 6,88</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>9,18; 12,61</t>
+          <t>9,34; 12,65</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>6,03; 9,32</t>
+          <t>6,08; 9,55</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>1,74; 11,9</t>
+          <t>6,63; 10,12</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>28,85%</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,58%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>18,09; 32,01</t>
+          <t>17,97; 32,02</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>16,38; 30,12</t>
+          <t>16,15; 29,7</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-5,12; 34,21</t>
+          <t>21,57; 36,35</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>15,6; 24,48</t>
+          <t>15,5; 24,19</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>6,23; 15,09</t>
+          <t>6,57; 15,21</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>6,87; 24,0</t>
+          <t>4,48; 12,12</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>18,0; 25,78</t>
+          <t>18,55; 26,01</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>12,01; 19,11</t>
+          <t>11,98; 19,52</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>3,46; 24,17</t>
+          <t>13,19; 20,79</t>
         </is>
       </c>
     </row>
